--- a/docs/hub/estate/Faculty of Health and Education/Teaching Nursing and Care/Module team contacts 1052-53.xlsx
+++ b/docs/hub/estate/Faculty of Health and Education/Teaching Nursing and Care/Module team contacts 1052-53.xlsx
@@ -968,7 +968,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
